--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260625.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260625.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>17.78%</t>
+          <t>17.62%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>74,600,000</t>
+          <t>75,000,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.66%</t>
+          <t>7.65%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.08%</t>
+          <t>6.46%</t>
         </is>
       </c>
     </row>
@@ -682,51 +682,51 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.81%</t>
+          <t>5.22%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>3,250,000</t>
+          <t>38,800,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.74%</t>
+          <t>4.87%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>38,800,000</t>
+          <t>3,250,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.59%</t>
+          <t>4.65%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.35%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.89%</t>
+          <t>3.71%</t>
         </is>
       </c>
     </row>
@@ -792,73 +792,73 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>3.54%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>4,200,000</t>
+          <t>2,100,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>2.86%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>2,100,000</t>
+          <t>2,430,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.75%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2,430,000</t>
+          <t>3,700,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.22%</t>
         </is>
       </c>
     </row>
@@ -902,29 +902,29 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>830,000</t>
+          <t>4,500,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
@@ -946,95 +946,95 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>4,500,000</t>
+          <t>830,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>16,350,000</t>
+          <t>1,240,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.58%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1,240,000</t>
+          <t>1,560,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>1,560,000</t>
+          <t>13,850,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>430,000</t>
+          <t>450,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
@@ -1100,24 +1100,24 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>279,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,83 +1129,83 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>279,000</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>1,968,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>1,800,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>1,950,000</t>
+          <t>390,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,22 +1217,22 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>390,000</t>
+          <t>1,950,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
@@ -1298,134 +1298,134 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>500,000</t>
+          <t>450,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>450,000</t>
+          <t>795,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>400,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>795,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1452,51 +1452,51 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.34%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.33%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
@@ -1540,95 +1540,95 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>160,000</t>
+          <t>1,010,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>1,010,000</t>
+          <t>500,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.14%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>600,000</t>
+          <t>450,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>450,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>4,523,475,393</t>
+          <t>3,213,906,209</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>-27,843,602</t>
+          <t>1,375,109,400</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
